--- a/public/template/FORMAT IMPORT PRODUK.xlsx
+++ b/public/template/FORMAT IMPORT PRODUK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIT-PROJECTS\ga_store\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9157D0-FACE-45C6-90F2-77D3F8862110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92CE222-2828-49A3-9F57-225C8BE5C615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8E00303F-0464-49D3-806C-EE89A8677154}"/>
   </bookViews>
@@ -137,12 +137,61 @@
         </r>
       </text>
     </comment>
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{DCCC2748-E7D9-4BD7-9AE3-F8F5DE1E2C65}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>B I T:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+- isi 1 untuk memunculkan di store
+- isi 0 jika tidak muncul di store</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{A8AA77B1-7C24-409E-97D9-A6C16E009FFC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>B I T:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+- penanggung jawab</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>kode_barang</t>
   </si>
@@ -186,9 +235,6 @@
     <t>special_order</t>
   </si>
   <si>
-    <t>BP</t>
-  </si>
-  <si>
     <t>Pulpen Faber Castell</t>
   </si>
   <si>
@@ -223,6 +269,45 @@
   </si>
   <si>
     <t>PCS</t>
+  </si>
+  <si>
+    <t>lokasi</t>
+  </si>
+  <si>
+    <t>max_stock</t>
+  </si>
+  <si>
+    <t>min_stock</t>
+  </si>
+  <si>
+    <t>show</t>
+  </si>
+  <si>
+    <t>responsibility</t>
+  </si>
+  <si>
+    <t>no_asset</t>
+  </si>
+  <si>
+    <t>nomor_barang</t>
+  </si>
+  <si>
+    <t>tahun</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Dasep</t>
+  </si>
+  <si>
+    <t>FSP01</t>
+  </si>
+  <si>
+    <t>BRG001</t>
+  </si>
+  <si>
+    <t>BP03</t>
   </si>
 </sst>
 </file>
@@ -231,9 +316,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,6 +354,19 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -301,7 +399,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -318,6 +416,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -617,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{876A2B24-6876-457A-AC1A-415949F123F1}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.1796875" bestFit="1" customWidth="1"/>
@@ -635,11 +737,16 @@
     <col min="13" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -683,67 +790,115 @@
       <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="P1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
       </c>
       <c r="L2">
         <v>1500</v>
       </c>
       <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
         <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
       </c>
       <c r="O2">
         <v>1</v>
       </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2">
+        <v>2022</v>
+      </c>
+      <c r="V2">
+        <v>10</v>
+      </c>
+      <c r="W2">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
